--- a/reports/一级子公司B_现金流量表_2025-02.xlsx
+++ b/reports/一级子公司B_现金流量表_2025-02.xlsx
@@ -1957,16 +1957,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
-      <c r="G3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
+      <c r="F3" s="28" t="n"/>
+      <c r="G3" s="28" t="n"/>
       <c r="I3" s="5" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1996,10 +1988,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>41184000</v>
+        <v>41036053</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>82368000</v>
+        <v>82257241</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2030,10 +2022,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>896348</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>1789305</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2063,10 +2055,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>443945</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>889099</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2096,10 +2088,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>224172</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>448046</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2129,10 +2121,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>177694</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>355356</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2162,10 +2154,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>134287</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>268799</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2195,10 +2187,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>89062</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>177856</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2228,10 +2220,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>66946</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>134160</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2261,10 +2253,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>44673</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>89141</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2294,10 +2286,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>111233</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>222990</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2327,10 +2319,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>56277</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>112312</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2360,10 +2352,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>35297</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>70717</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2393,10 +2385,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>132000</v>
+        <v>132660</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>264000</v>
+        <v>265018</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2426,10 +2418,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>792000</v>
+        <v>788230</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>1584000</v>
+        <v>1577131</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2546,7 +2538,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>42108000</v>
+        <v>44236877</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2577,10 +2569,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>21120000</v>
+        <v>21082364</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>42240000</v>
+        <v>42263616</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2610,10 +2602,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>298386</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>595395</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2643,10 +2635,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>222133</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>445179</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2676,10 +2668,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>149444</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>298423</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2709,10 +2701,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>110985</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>222174</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2742,10 +2734,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>74700</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>149374</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2775,10 +2767,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>55849</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>111633</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2808,10 +2800,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>7480000</v>
+        <v>7498053</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>14960000</v>
+        <v>15015322</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2841,10 +2833,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>2816000</v>
+        <v>2813494</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>5632000</v>
+        <v>5616573</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2874,10 +2866,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>1584000</v>
+        <v>1582849</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>3168000</v>
+        <v>3172733</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2936,7 +2928,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>33000000</v>
+        <v>33888257</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2967,7 +2959,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>9108000</v>
+        <v>10348620</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -3093,10 +3085,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>60000</v>
+        <v>60198</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>120000</v>
+        <v>120495</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3159,10 +3151,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>600000</v>
+        <v>600218</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>1200000</v>
+        <v>1202829</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3192,10 +3184,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>360000</v>
+        <v>360449</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>720000</v>
+        <v>719247</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3225,7 +3217,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>660000</v>
+        <v>660416</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3256,10 +3248,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>6000000</v>
+        <v>6023529</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>12000000</v>
+        <v>12021083</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3289,10 +3281,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>900000</v>
+        <v>895764</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>1800000</v>
+        <v>1794681</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3322,10 +3314,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>4200000</v>
+        <v>4220996</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>8400000</v>
+        <v>8432292</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3454,10 +3446,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>140000</v>
+        <v>140201</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>280000</v>
+        <v>280871</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3487,7 +3479,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>6140000</v>
+        <v>6163730</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3518,7 +3510,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-5480000</v>
+        <v>-5503314</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3578,10 +3570,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>1200000</v>
+        <v>1194926</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>2400000</v>
+        <v>2394779</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3644,10 +3636,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>2000000</v>
+        <v>1990037</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>4000000</v>
+        <v>3983795</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3677,10 +3669,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>2000000</v>
+        <v>2009166</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>4000000</v>
+        <v>4017575</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3710,10 +3702,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>60000</v>
+        <v>59778</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>120000</v>
+        <v>119487</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3743,7 +3735,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>3260000</v>
+        <v>3244741</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3774,10 +3766,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>1600000</v>
+        <v>1598527</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>3200000</v>
+        <v>3191166</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3807,10 +3799,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>1600000</v>
+        <v>1598887</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>3200000</v>
+        <v>3204863</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3840,10 +3832,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>280000</v>
+        <v>280627</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>560000</v>
+        <v>559933</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3902,10 +3894,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>240000</v>
+        <v>241077</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>480000</v>
+        <v>481233</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3935,10 +3927,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>35000</v>
+        <v>34827</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>70000</v>
+        <v>69750</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3968,7 +3960,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>1915000</v>
+        <v>1913981</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3999,7 +3991,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>1345000</v>
+        <v>1330760</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -4059,7 +4051,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>4973000</v>
+        <v>6176066</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -4090,7 +4082,9 @@
         </is>
       </c>
       <c r="F69" s="23" t="n"/>
-      <c r="G69" s="20" t="n"/>
+      <c r="G69" s="20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
@@ -4119,7 +4113,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>4973000</v>
+        <v>6176066</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
